--- a/Templates/Tables/ResInfo/ResInfoTable.xlsx
+++ b/Templates/Tables/ResInfo/ResInfoTable.xlsx
@@ -303,7 +303,7 @@
     <col customWidth="1" min="1" max="26" width="14.38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -340,7 +340,7 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -377,7 +377,7 @@
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
@@ -402,7 +402,7 @@
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="1"/>
@@ -427,7 +427,7 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="1"/>
@@ -452,7 +452,7 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="1"/>
@@ -477,7 +477,7 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
@@ -502,7 +502,7 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
@@ -527,7 +527,7 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
@@ -552,7 +552,7 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
@@ -577,7 +577,7 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="1"/>
@@ -602,7 +602,7 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="1"/>
@@ -627,7 +627,7 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="1"/>
@@ -652,7 +652,7 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
@@ -677,7 +677,7 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="1"/>
@@ -702,7 +702,7 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
@@ -727,7 +727,7 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="1"/>
@@ -752,7 +752,7 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="1"/>
@@ -777,7 +777,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -802,7 +802,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
       <c r="C20" s="1"/>
@@ -827,7 +827,7 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="1"/>
@@ -852,7 +852,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="1"/>
@@ -877,7 +877,7 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="1"/>
@@ -902,7 +902,7 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="1"/>
@@ -927,7 +927,7 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" s="1"/>
@@ -952,7 +952,7 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="1"/>
@@ -977,7 +977,7 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="1"/>
@@ -1002,7 +1002,7 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="1"/>
@@ -1027,7 +1027,7 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" s="1"/>
@@ -1052,7 +1052,7 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="1"/>
@@ -1077,7 +1077,7 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -1102,7 +1102,7 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="1"/>
@@ -1127,7 +1127,7 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
       <c r="C33" s="1"/>
@@ -1152,7 +1152,7 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="2"/>
       <c r="C34" s="1"/>
@@ -1177,7 +1177,7 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="2"/>
       <c r="C35" s="1"/>
@@ -1202,7 +1202,7 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="2"/>
       <c r="C36" s="1"/>
@@ -1227,7 +1227,7 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="2"/>
       <c r="C37" s="1"/>
@@ -1252,7 +1252,7 @@
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="2"/>
       <c r="C38" s="1"/>
@@ -1277,7 +1277,7 @@
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="C39" s="1"/>
@@ -1302,7 +1302,7 @@
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
       <c r="C40" s="1"/>
@@ -1327,7 +1327,7 @@
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="2"/>
       <c r="C41" s="1"/>
@@ -1352,7 +1352,7 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="2"/>
       <c r="C42" s="1"/>
@@ -1377,7 +1377,7 @@
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="2"/>
       <c r="C43" s="1"/>
@@ -1402,7 +1402,7 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="1"/>
@@ -1427,7 +1427,7 @@
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -1452,7 +1452,7 @@
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="1"/>
@@ -1477,7 +1477,7 @@
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="1"/>
@@ -1502,7 +1502,7 @@
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="1"/>
@@ -1527,7 +1527,7 @@
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="1"/>
@@ -1552,7 +1552,7 @@
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="1"/>
@@ -1577,7 +1577,7 @@
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="1"/>
@@ -1602,7 +1602,7 @@
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="1"/>
@@ -1627,7 +1627,7 @@
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="1"/>
@@ -1652,7 +1652,7 @@
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="1"/>
@@ -1677,7 +1677,7 @@
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="1"/>
@@ -1702,7 +1702,7 @@
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="1"/>
@@ -1727,7 +1727,7 @@
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="1"/>
@@ -1752,7 +1752,7 @@
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="1"/>
@@ -1777,7 +1777,7 @@
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="1"/>
@@ -1802,7 +1802,7 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="1"/>
@@ -1827,7 +1827,7 @@
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="1"/>
@@ -1852,7 +1852,7 @@
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="1"/>
@@ -1877,7 +1877,7 @@
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="1"/>
@@ -1902,7 +1902,7 @@
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
       <c r="C64" s="1"/>
@@ -1927,7 +1927,7 @@
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="1"/>
@@ -1952,7 +1952,7 @@
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="1"/>
@@ -1977,7 +1977,7 @@
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="1"/>
@@ -2002,7 +2002,7 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="1"/>
@@ -2027,7 +2027,7 @@
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="1"/>
@@ -2052,7 +2052,7 @@
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="1"/>
@@ -2077,7 +2077,7 @@
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="1"/>
@@ -2102,7 +2102,7 @@
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="1"/>
@@ -2127,7 +2127,7 @@
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="1"/>
@@ -2152,7 +2152,7 @@
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="1"/>
@@ -2177,7 +2177,7 @@
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="1"/>
@@ -2202,7 +2202,7 @@
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="1"/>
@@ -2227,7 +2227,7 @@
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="2"/>
       <c r="C77" s="1"/>
@@ -2252,7 +2252,7 @@
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="1"/>
@@ -2277,7 +2277,7 @@
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="1"/>
@@ -2302,7 +2302,7 @@
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="1"/>
@@ -2327,7 +2327,7 @@
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="1"/>
@@ -2352,7 +2352,7 @@
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="1"/>
@@ -2377,7 +2377,7 @@
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="1"/>
@@ -2402,7 +2402,7 @@
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="1"/>
@@ -2427,7 +2427,7 @@
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="1"/>
@@ -2452,7 +2452,7 @@
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="1"/>
@@ -2477,7 +2477,7 @@
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="1"/>
@@ -2502,7 +2502,7 @@
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="1"/>
@@ -2527,7 +2527,7 @@
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="1"/>
@@ -2552,7 +2552,7 @@
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="1"/>
@@ -2577,7 +2577,7 @@
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="1"/>
@@ -2602,7 +2602,7 @@
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="1"/>
@@ -2627,7 +2627,7 @@
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="1"/>
@@ -2652,7 +2652,7 @@
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="1"/>
@@ -2677,7 +2677,7 @@
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
       <c r="C95" s="1"/>
@@ -2702,7 +2702,7 @@
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="1"/>
@@ -2727,7 +2727,7 @@
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="1"/>
@@ -2752,7 +2752,7 @@
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="1"/>
@@ -2777,7 +2777,7 @@
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="1"/>
@@ -2802,7 +2802,7 @@
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="1"/>
@@ -2827,7 +2827,7 @@
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="1"/>
@@ -2852,7 +2852,7 @@
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="1"/>
@@ -2877,7 +2877,7 @@
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="2"/>
       <c r="C103" s="1"/>
@@ -2902,7 +2902,7 @@
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
       <c r="C104" s="1"/>
@@ -2927,7 +2927,7 @@
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="1"/>
@@ -2952,7 +2952,7 @@
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="1"/>
@@ -2977,7 +2977,7 @@
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="1"/>
@@ -3002,7 +3002,7 @@
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="1"/>
@@ -3027,7 +3027,7 @@
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="1"/>
@@ -3052,7 +3052,7 @@
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="1"/>
@@ -3077,7 +3077,7 @@
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="1"/>
@@ -3102,7 +3102,7 @@
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="1"/>
@@ -3127,7 +3127,7 @@
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="1"/>
@@ -3152,7 +3152,7 @@
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="1"/>
@@ -3177,7 +3177,7 @@
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="2"/>
       <c r="C115" s="1"/>
@@ -3202,7 +3202,7 @@
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="2"/>
       <c r="C116" s="1"/>
@@ -3227,7 +3227,7 @@
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="2"/>
       <c r="C117" s="1"/>
@@ -3252,7 +3252,7 @@
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
       <c r="C118" s="1"/>
@@ -3277,7 +3277,7 @@
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="2"/>
       <c r="C119" s="1"/>
@@ -3302,7 +3302,7 @@
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
       <c r="C120" s="1"/>
@@ -3327,7 +3327,7 @@
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="2"/>
       <c r="C121" s="1"/>
@@ -3352,7 +3352,7 @@
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
       <c r="C122" s="1"/>
@@ -3377,7 +3377,7 @@
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="1"/>
@@ -3402,7 +3402,7 @@
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="2"/>
       <c r="C124" s="1"/>
@@ -3427,7 +3427,7 @@
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="2"/>
       <c r="C125" s="1"/>
@@ -3452,7 +3452,7 @@
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="2"/>
       <c r="C126" s="1"/>
@@ -3477,7 +3477,7 @@
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="1"/>
@@ -3502,7 +3502,7 @@
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="2"/>
       <c r="C128" s="1"/>
@@ -3527,7 +3527,7 @@
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="1"/>
@@ -3552,7 +3552,7 @@
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="2"/>
       <c r="C130" s="1"/>
@@ -3577,7 +3577,7 @@
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="2"/>
       <c r="C131" s="1"/>
@@ -3602,7 +3602,7 @@
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="2"/>
       <c r="C132" s="1"/>
@@ -3627,7 +3627,7 @@
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="1"/>
@@ -3652,7 +3652,7 @@
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="2"/>
       <c r="C134" s="1"/>
@@ -3677,7 +3677,7 @@
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="2"/>
       <c r="C135" s="1"/>
@@ -3702,7 +3702,7 @@
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="1"/>
@@ -3727,7 +3727,7 @@
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="2"/>
       <c r="C137" s="1"/>
@@ -3752,7 +3752,7 @@
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="1"/>
@@ -3777,7 +3777,7 @@
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="2"/>
       <c r="C139" s="1"/>
@@ -3802,7 +3802,7 @@
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="2"/>
       <c r="C140" s="1"/>
@@ -3827,7 +3827,7 @@
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="2"/>
       <c r="C141" s="1"/>
@@ -3852,7 +3852,7 @@
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="2"/>
       <c r="C142" s="1"/>
@@ -3877,7 +3877,7 @@
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="1"/>
@@ -3902,7 +3902,7 @@
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
       <c r="C144" s="1"/>
@@ -3927,7 +3927,7 @@
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="2"/>
       <c r="C145" s="1"/>
@@ -3952,7 +3952,7 @@
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="1"/>
@@ -3977,7 +3977,7 @@
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="1"/>
@@ -4002,7 +4002,7 @@
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="2"/>
       <c r="C148" s="1"/>
@@ -4027,7 +4027,7 @@
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="1"/>
@@ -4052,7 +4052,7 @@
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="1"/>
@@ -4077,7 +4077,7 @@
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="1"/>
@@ -4102,7 +4102,7 @@
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="1"/>
@@ -4127,7 +4127,7 @@
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="1"/>
@@ -4152,7 +4152,7 @@
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="1"/>
@@ -4177,7 +4177,7 @@
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="1"/>
@@ -4202,7 +4202,7 @@
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="1"/>
@@ -4227,7 +4227,7 @@
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="1"/>
@@ -4252,7 +4252,7 @@
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="1"/>
@@ -4277,7 +4277,7 @@
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="1"/>
@@ -4302,7 +4302,7 @@
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="2"/>
       <c r="C160" s="1"/>
@@ -4327,7 +4327,7 @@
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="2"/>
       <c r="C161" s="1"/>
@@ -4352,7 +4352,7 @@
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="2"/>
       <c r="C162" s="1"/>
@@ -4377,7 +4377,7 @@
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="1"/>
@@ -4402,7 +4402,7 @@
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="1"/>
@@ -4427,7 +4427,7 @@
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="2"/>
       <c r="C165" s="1"/>
@@ -4452,7 +4452,7 @@
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="2"/>
       <c r="C166" s="1"/>
@@ -4477,7 +4477,7 @@
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="1"/>
@@ -4502,7 +4502,7 @@
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="1"/>
@@ -4527,7 +4527,7 @@
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="1"/>
@@ -4552,7 +4552,7 @@
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="1"/>
@@ -4577,7 +4577,7 @@
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="1"/>
@@ -4602,7 +4602,7 @@
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="1"/>
@@ -4627,7 +4627,7 @@
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="1"/>
@@ -4652,7 +4652,7 @@
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="1"/>
@@ -4677,7 +4677,7 @@
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="1"/>
@@ -4702,7 +4702,7 @@
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="1"/>
@@ -4727,7 +4727,7 @@
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="1"/>
@@ -4752,7 +4752,7 @@
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="1"/>
@@ -4777,7 +4777,7 @@
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="1"/>
@@ -4802,7 +4802,7 @@
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="1"/>
@@ -4827,7 +4827,7 @@
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="1"/>
@@ -4852,7 +4852,7 @@
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="2"/>
       <c r="C182" s="1"/>
@@ -4877,7 +4877,7 @@
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="2"/>
       <c r="C183" s="1"/>
@@ -4902,7 +4902,7 @@
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="2"/>
       <c r="C184" s="1"/>
@@ -4927,7 +4927,7 @@
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="2"/>
       <c r="C185" s="1"/>
@@ -4952,7 +4952,7 @@
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="2"/>
       <c r="C186" s="1"/>
@@ -4977,7 +4977,7 @@
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="2"/>
       <c r="C187" s="1"/>
@@ -5002,7 +5002,7 @@
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="2"/>
       <c r="C188" s="1"/>
@@ -5027,7 +5027,7 @@
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="2"/>
       <c r="C189" s="1"/>
@@ -5052,7 +5052,7 @@
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="2"/>
       <c r="C190" s="1"/>
@@ -5077,7 +5077,7 @@
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="2"/>
       <c r="C191" s="1"/>
@@ -5102,7 +5102,7 @@
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="2"/>
       <c r="C192" s="1"/>
@@ -5127,7 +5127,7 @@
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="2"/>
       <c r="C193" s="1"/>
@@ -5152,7 +5152,7 @@
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="2"/>
       <c r="C194" s="1"/>
@@ -5177,7 +5177,7 @@
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="2"/>
       <c r="C195" s="1"/>
@@ -5202,7 +5202,7 @@
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="2"/>
       <c r="C196" s="1"/>
@@ -5227,7 +5227,7 @@
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="2"/>
       <c r="C197" s="1"/>
@@ -5252,7 +5252,7 @@
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="2"/>
       <c r="C198" s="1"/>
@@ -5277,7 +5277,7 @@
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="2"/>
       <c r="C199" s="1"/>
@@ -5302,7 +5302,7 @@
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="2"/>
       <c r="C200" s="1"/>
@@ -5327,7 +5327,7 @@
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="2"/>
       <c r="C201" s="1"/>
@@ -5352,7 +5352,7 @@
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="2"/>
       <c r="C202" s="1"/>
@@ -5377,7 +5377,7 @@
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="2"/>
       <c r="C203" s="1"/>
@@ -5402,7 +5402,7 @@
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="2"/>
       <c r="C204" s="1"/>
@@ -5427,7 +5427,7 @@
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="2"/>
       <c r="C205" s="1"/>
@@ -5452,7 +5452,7 @@
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="2"/>
       <c r="C206" s="1"/>
@@ -5477,7 +5477,7 @@
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="2"/>
       <c r="C207" s="1"/>
@@ -5502,7 +5502,7 @@
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="2"/>
       <c r="C208" s="1"/>
@@ -5527,7 +5527,7 @@
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="2"/>
       <c r="C209" s="1"/>
@@ -5552,7 +5552,7 @@
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="2"/>
       <c r="C210" s="1"/>
@@ -5577,7 +5577,7 @@
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="2"/>
       <c r="C211" s="1"/>
@@ -5602,7 +5602,7 @@
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="2"/>
       <c r="C212" s="1"/>
@@ -5627,7 +5627,7 @@
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="2"/>
       <c r="C213" s="1"/>
@@ -5652,7 +5652,7 @@
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="2"/>
       <c r="C214" s="1"/>
@@ -5677,7 +5677,7 @@
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="2"/>
       <c r="C215" s="1"/>
@@ -5702,7 +5702,7 @@
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="2"/>
       <c r="C216" s="1"/>
@@ -5727,7 +5727,7 @@
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="2"/>
       <c r="C217" s="1"/>
@@ -5752,7 +5752,7 @@
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="2"/>
       <c r="C218" s="1"/>
@@ -5777,7 +5777,7 @@
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="2"/>
       <c r="C219" s="1"/>
@@ -5802,7 +5802,7 @@
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="2"/>
       <c r="C220" s="1"/>
@@ -5827,786 +5827,786 @@
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.0" customHeight="1"/>
+    <row r="222" ht="15.0" customHeight="1"/>
+    <row r="223" ht="15.0" customHeight="1"/>
+    <row r="224" ht="15.0" customHeight="1"/>
+    <row r="225" ht="15.0" customHeight="1"/>
+    <row r="226" ht="15.0" customHeight="1"/>
+    <row r="227" ht="15.0" customHeight="1"/>
+    <row r="228" ht="15.0" customHeight="1"/>
+    <row r="229" ht="15.0" customHeight="1"/>
+    <row r="230" ht="15.0" customHeight="1"/>
+    <row r="231" ht="15.0" customHeight="1"/>
+    <row r="232" ht="15.0" customHeight="1"/>
+    <row r="233" ht="15.0" customHeight="1"/>
+    <row r="234" ht="15.0" customHeight="1"/>
+    <row r="235" ht="15.0" customHeight="1"/>
+    <row r="236" ht="15.0" customHeight="1"/>
+    <row r="237" ht="15.0" customHeight="1"/>
+    <row r="238" ht="15.0" customHeight="1"/>
+    <row r="239" ht="15.0" customHeight="1"/>
+    <row r="240" ht="15.0" customHeight="1"/>
+    <row r="241" ht="15.0" customHeight="1"/>
+    <row r="242" ht="15.0" customHeight="1"/>
+    <row r="243" ht="15.0" customHeight="1"/>
+    <row r="244" ht="15.0" customHeight="1"/>
+    <row r="245" ht="15.0" customHeight="1"/>
+    <row r="246" ht="15.0" customHeight="1"/>
+    <row r="247" ht="15.0" customHeight="1"/>
+    <row r="248" ht="15.0" customHeight="1"/>
+    <row r="249" ht="15.0" customHeight="1"/>
+    <row r="250" ht="15.0" customHeight="1"/>
+    <row r="251" ht="15.0" customHeight="1"/>
+    <row r="252" ht="15.0" customHeight="1"/>
+    <row r="253" ht="15.0" customHeight="1"/>
+    <row r="254" ht="15.0" customHeight="1"/>
+    <row r="255" ht="15.0" customHeight="1"/>
+    <row r="256" ht="15.0" customHeight="1"/>
+    <row r="257" ht="15.0" customHeight="1"/>
+    <row r="258" ht="15.0" customHeight="1"/>
+    <row r="259" ht="15.0" customHeight="1"/>
+    <row r="260" ht="15.0" customHeight="1"/>
+    <row r="261" ht="15.0" customHeight="1"/>
+    <row r="262" ht="15.0" customHeight="1"/>
+    <row r="263" ht="15.0" customHeight="1"/>
+    <row r="264" ht="15.0" customHeight="1"/>
+    <row r="265" ht="15.0" customHeight="1"/>
+    <row r="266" ht="15.0" customHeight="1"/>
+    <row r="267" ht="15.0" customHeight="1"/>
+    <row r="268" ht="15.0" customHeight="1"/>
+    <row r="269" ht="15.0" customHeight="1"/>
+    <row r="270" ht="15.0" customHeight="1"/>
+    <row r="271" ht="15.0" customHeight="1"/>
+    <row r="272" ht="15.0" customHeight="1"/>
+    <row r="273" ht="15.0" customHeight="1"/>
+    <row r="274" ht="15.0" customHeight="1"/>
+    <row r="275" ht="15.0" customHeight="1"/>
+    <row r="276" ht="15.0" customHeight="1"/>
+    <row r="277" ht="15.0" customHeight="1"/>
+    <row r="278" ht="15.0" customHeight="1"/>
+    <row r="279" ht="15.0" customHeight="1"/>
+    <row r="280" ht="15.0" customHeight="1"/>
+    <row r="281" ht="15.0" customHeight="1"/>
+    <row r="282" ht="15.0" customHeight="1"/>
+    <row r="283" ht="15.0" customHeight="1"/>
+    <row r="284" ht="15.0" customHeight="1"/>
+    <row r="285" ht="15.0" customHeight="1"/>
+    <row r="286" ht="15.0" customHeight="1"/>
+    <row r="287" ht="15.0" customHeight="1"/>
+    <row r="288" ht="15.0" customHeight="1"/>
+    <row r="289" ht="15.0" customHeight="1"/>
+    <row r="290" ht="15.0" customHeight="1"/>
+    <row r="291" ht="15.0" customHeight="1"/>
+    <row r="292" ht="15.0" customHeight="1"/>
+    <row r="293" ht="15.0" customHeight="1"/>
+    <row r="294" ht="15.0" customHeight="1"/>
+    <row r="295" ht="15.0" customHeight="1"/>
+    <row r="296" ht="15.0" customHeight="1"/>
+    <row r="297" ht="15.0" customHeight="1"/>
+    <row r="298" ht="15.0" customHeight="1"/>
+    <row r="299" ht="15.0" customHeight="1"/>
+    <row r="300" ht="15.0" customHeight="1"/>
+    <row r="301" ht="15.0" customHeight="1"/>
+    <row r="302" ht="15.0" customHeight="1"/>
+    <row r="303" ht="15.0" customHeight="1"/>
+    <row r="304" ht="15.0" customHeight="1"/>
+    <row r="305" ht="15.0" customHeight="1"/>
+    <row r="306" ht="15.0" customHeight="1"/>
+    <row r="307" ht="15.0" customHeight="1"/>
+    <row r="308" ht="15.0" customHeight="1"/>
+    <row r="309" ht="15.0" customHeight="1"/>
+    <row r="310" ht="15.0" customHeight="1"/>
+    <row r="311" ht="15.0" customHeight="1"/>
+    <row r="312" ht="15.0" customHeight="1"/>
+    <row r="313" ht="15.0" customHeight="1"/>
+    <row r="314" ht="15.0" customHeight="1"/>
+    <row r="315" ht="15.0" customHeight="1"/>
+    <row r="316" ht="15.0" customHeight="1"/>
+    <row r="317" ht="15.0" customHeight="1"/>
+    <row r="318" ht="15.0" customHeight="1"/>
+    <row r="319" ht="15.0" customHeight="1"/>
+    <row r="320" ht="15.0" customHeight="1"/>
+    <row r="321" ht="15.0" customHeight="1"/>
+    <row r="322" ht="15.0" customHeight="1"/>
+    <row r="323" ht="15.0" customHeight="1"/>
+    <row r="324" ht="15.0" customHeight="1"/>
+    <row r="325" ht="15.0" customHeight="1"/>
+    <row r="326" ht="15.0" customHeight="1"/>
+    <row r="327" ht="15.0" customHeight="1"/>
+    <row r="328" ht="15.0" customHeight="1"/>
+    <row r="329" ht="15.0" customHeight="1"/>
+    <row r="330" ht="15.0" customHeight="1"/>
+    <row r="331" ht="15.0" customHeight="1"/>
+    <row r="332" ht="15.0" customHeight="1"/>
+    <row r="333" ht="15.0" customHeight="1"/>
+    <row r="334" ht="15.0" customHeight="1"/>
+    <row r="335" ht="15.0" customHeight="1"/>
+    <row r="336" ht="15.0" customHeight="1"/>
+    <row r="337" ht="15.0" customHeight="1"/>
+    <row r="338" ht="15.0" customHeight="1"/>
+    <row r="339" ht="15.0" customHeight="1"/>
+    <row r="340" ht="15.0" customHeight="1"/>
+    <row r="341" ht="15.0" customHeight="1"/>
+    <row r="342" ht="15.0" customHeight="1"/>
+    <row r="343" ht="15.0" customHeight="1"/>
+    <row r="344" ht="15.0" customHeight="1"/>
+    <row r="345" ht="15.0" customHeight="1"/>
+    <row r="346" ht="15.0" customHeight="1"/>
+    <row r="347" ht="15.0" customHeight="1"/>
+    <row r="348" ht="15.0" customHeight="1"/>
+    <row r="349" ht="15.0" customHeight="1"/>
+    <row r="350" ht="15.0" customHeight="1"/>
+    <row r="351" ht="15.0" customHeight="1"/>
+    <row r="352" ht="15.0" customHeight="1"/>
+    <row r="353" ht="15.0" customHeight="1"/>
+    <row r="354" ht="15.0" customHeight="1"/>
+    <row r="355" ht="15.0" customHeight="1"/>
+    <row r="356" ht="15.0" customHeight="1"/>
+    <row r="357" ht="15.0" customHeight="1"/>
+    <row r="358" ht="15.0" customHeight="1"/>
+    <row r="359" ht="15.0" customHeight="1"/>
+    <row r="360" ht="15.0" customHeight="1"/>
+    <row r="361" ht="15.0" customHeight="1"/>
+    <row r="362" ht="15.0" customHeight="1"/>
+    <row r="363" ht="15.0" customHeight="1"/>
+    <row r="364" ht="15.0" customHeight="1"/>
+    <row r="365" ht="15.0" customHeight="1"/>
+    <row r="366" ht="15.0" customHeight="1"/>
+    <row r="367" ht="15.0" customHeight="1"/>
+    <row r="368" ht="15.0" customHeight="1"/>
+    <row r="369" ht="15.0" customHeight="1"/>
+    <row r="370" ht="15.0" customHeight="1"/>
+    <row r="371" ht="15.0" customHeight="1"/>
+    <row r="372" ht="15.0" customHeight="1"/>
+    <row r="373" ht="15.0" customHeight="1"/>
+    <row r="374" ht="15.0" customHeight="1"/>
+    <row r="375" ht="15.0" customHeight="1"/>
+    <row r="376" ht="15.0" customHeight="1"/>
+    <row r="377" ht="15.0" customHeight="1"/>
+    <row r="378" ht="15.0" customHeight="1"/>
+    <row r="379" ht="15.0" customHeight="1"/>
+    <row r="380" ht="15.0" customHeight="1"/>
+    <row r="381" ht="15.0" customHeight="1"/>
+    <row r="382" ht="15.0" customHeight="1"/>
+    <row r="383" ht="15.0" customHeight="1"/>
+    <row r="384" ht="15.0" customHeight="1"/>
+    <row r="385" ht="15.0" customHeight="1"/>
+    <row r="386" ht="15.0" customHeight="1"/>
+    <row r="387" ht="15.0" customHeight="1"/>
+    <row r="388" ht="15.0" customHeight="1"/>
+    <row r="389" ht="15.0" customHeight="1"/>
+    <row r="390" ht="15.0" customHeight="1"/>
+    <row r="391" ht="15.0" customHeight="1"/>
+    <row r="392" ht="15.0" customHeight="1"/>
+    <row r="393" ht="15.0" customHeight="1"/>
+    <row r="394" ht="15.0" customHeight="1"/>
+    <row r="395" ht="15.0" customHeight="1"/>
+    <row r="396" ht="15.0" customHeight="1"/>
+    <row r="397" ht="15.0" customHeight="1"/>
+    <row r="398" ht="15.0" customHeight="1"/>
+    <row r="399" ht="15.0" customHeight="1"/>
+    <row r="400" ht="15.0" customHeight="1"/>
+    <row r="401" ht="15.0" customHeight="1"/>
+    <row r="402" ht="15.0" customHeight="1"/>
+    <row r="403" ht="15.0" customHeight="1"/>
+    <row r="404" ht="15.0" customHeight="1"/>
+    <row r="405" ht="15.0" customHeight="1"/>
+    <row r="406" ht="15.0" customHeight="1"/>
+    <row r="407" ht="15.0" customHeight="1"/>
+    <row r="408" ht="15.0" customHeight="1"/>
+    <row r="409" ht="15.0" customHeight="1"/>
+    <row r="410" ht="15.0" customHeight="1"/>
+    <row r="411" ht="15.0" customHeight="1"/>
+    <row r="412" ht="15.0" customHeight="1"/>
+    <row r="413" ht="15.0" customHeight="1"/>
+    <row r="414" ht="15.0" customHeight="1"/>
+    <row r="415" ht="15.0" customHeight="1"/>
+    <row r="416" ht="15.0" customHeight="1"/>
+    <row r="417" ht="15.0" customHeight="1"/>
+    <row r="418" ht="15.0" customHeight="1"/>
+    <row r="419" ht="15.0" customHeight="1"/>
+    <row r="420" ht="15.0" customHeight="1"/>
+    <row r="421" ht="15.0" customHeight="1"/>
+    <row r="422" ht="15.0" customHeight="1"/>
+    <row r="423" ht="15.0" customHeight="1"/>
+    <row r="424" ht="15.0" customHeight="1"/>
+    <row r="425" ht="15.0" customHeight="1"/>
+    <row r="426" ht="15.0" customHeight="1"/>
+    <row r="427" ht="15.0" customHeight="1"/>
+    <row r="428" ht="15.0" customHeight="1"/>
+    <row r="429" ht="15.0" customHeight="1"/>
+    <row r="430" ht="15.0" customHeight="1"/>
+    <row r="431" ht="15.0" customHeight="1"/>
+    <row r="432" ht="15.0" customHeight="1"/>
+    <row r="433" ht="15.0" customHeight="1"/>
+    <row r="434" ht="15.0" customHeight="1"/>
+    <row r="435" ht="15.0" customHeight="1"/>
+    <row r="436" ht="15.0" customHeight="1"/>
+    <row r="437" ht="15.0" customHeight="1"/>
+    <row r="438" ht="15.0" customHeight="1"/>
+    <row r="439" ht="15.0" customHeight="1"/>
+    <row r="440" ht="15.0" customHeight="1"/>
+    <row r="441" ht="15.0" customHeight="1"/>
+    <row r="442" ht="15.0" customHeight="1"/>
+    <row r="443" ht="15.0" customHeight="1"/>
+    <row r="444" ht="15.0" customHeight="1"/>
+    <row r="445" ht="15.0" customHeight="1"/>
+    <row r="446" ht="15.0" customHeight="1"/>
+    <row r="447" ht="15.0" customHeight="1"/>
+    <row r="448" ht="15.0" customHeight="1"/>
+    <row r="449" ht="15.0" customHeight="1"/>
+    <row r="450" ht="15.0" customHeight="1"/>
+    <row r="451" ht="15.0" customHeight="1"/>
+    <row r="452" ht="15.0" customHeight="1"/>
+    <row r="453" ht="15.0" customHeight="1"/>
+    <row r="454" ht="15.0" customHeight="1"/>
+    <row r="455" ht="15.0" customHeight="1"/>
+    <row r="456" ht="15.0" customHeight="1"/>
+    <row r="457" ht="15.0" customHeight="1"/>
+    <row r="458" ht="15.0" customHeight="1"/>
+    <row r="459" ht="15.0" customHeight="1"/>
+    <row r="460" ht="15.0" customHeight="1"/>
+    <row r="461" ht="15.0" customHeight="1"/>
+    <row r="462" ht="15.0" customHeight="1"/>
+    <row r="463" ht="15.0" customHeight="1"/>
+    <row r="464" ht="15.0" customHeight="1"/>
+    <row r="465" ht="15.0" customHeight="1"/>
+    <row r="466" ht="15.0" customHeight="1"/>
+    <row r="467" ht="15.0" customHeight="1"/>
+    <row r="468" ht="15.0" customHeight="1"/>
+    <row r="469" ht="15.0" customHeight="1"/>
+    <row r="470" ht="15.0" customHeight="1"/>
+    <row r="471" ht="15.0" customHeight="1"/>
+    <row r="472" ht="15.0" customHeight="1"/>
+    <row r="473" ht="15.0" customHeight="1"/>
+    <row r="474" ht="15.0" customHeight="1"/>
+    <row r="475" ht="15.0" customHeight="1"/>
+    <row r="476" ht="15.0" customHeight="1"/>
+    <row r="477" ht="15.0" customHeight="1"/>
+    <row r="478" ht="15.0" customHeight="1"/>
+    <row r="479" ht="15.0" customHeight="1"/>
+    <row r="480" ht="15.0" customHeight="1"/>
+    <row r="481" ht="15.0" customHeight="1"/>
+    <row r="482" ht="15.0" customHeight="1"/>
+    <row r="483" ht="15.0" customHeight="1"/>
+    <row r="484" ht="15.0" customHeight="1"/>
+    <row r="485" ht="15.0" customHeight="1"/>
+    <row r="486" ht="15.0" customHeight="1"/>
+    <row r="487" ht="15.0" customHeight="1"/>
+    <row r="488" ht="15.0" customHeight="1"/>
+    <row r="489" ht="15.0" customHeight="1"/>
+    <row r="490" ht="15.0" customHeight="1"/>
+    <row r="491" ht="15.0" customHeight="1"/>
+    <row r="492" ht="15.0" customHeight="1"/>
+    <row r="493" ht="15.0" customHeight="1"/>
+    <row r="494" ht="15.0" customHeight="1"/>
+    <row r="495" ht="15.0" customHeight="1"/>
+    <row r="496" ht="15.0" customHeight="1"/>
+    <row r="497" ht="15.0" customHeight="1"/>
+    <row r="498" ht="15.0" customHeight="1"/>
+    <row r="499" ht="15.0" customHeight="1"/>
+    <row r="500" ht="15.0" customHeight="1"/>
+    <row r="501" ht="15.0" customHeight="1"/>
+    <row r="502" ht="15.0" customHeight="1"/>
+    <row r="503" ht="15.0" customHeight="1"/>
+    <row r="504" ht="15.0" customHeight="1"/>
+    <row r="505" ht="15.0" customHeight="1"/>
+    <row r="506" ht="15.0" customHeight="1"/>
+    <row r="507" ht="15.0" customHeight="1"/>
+    <row r="508" ht="15.0" customHeight="1"/>
+    <row r="509" ht="15.0" customHeight="1"/>
+    <row r="510" ht="15.0" customHeight="1"/>
+    <row r="511" ht="15.0" customHeight="1"/>
+    <row r="512" ht="15.0" customHeight="1"/>
+    <row r="513" ht="15.0" customHeight="1"/>
+    <row r="514" ht="15.0" customHeight="1"/>
+    <row r="515" ht="15.0" customHeight="1"/>
+    <row r="516" ht="15.0" customHeight="1"/>
+    <row r="517" ht="15.0" customHeight="1"/>
+    <row r="518" ht="15.0" customHeight="1"/>
+    <row r="519" ht="15.0" customHeight="1"/>
+    <row r="520" ht="15.0" customHeight="1"/>
+    <row r="521" ht="15.0" customHeight="1"/>
+    <row r="522" ht="15.0" customHeight="1"/>
+    <row r="523" ht="15.0" customHeight="1"/>
+    <row r="524" ht="15.0" customHeight="1"/>
+    <row r="525" ht="15.0" customHeight="1"/>
+    <row r="526" ht="15.0" customHeight="1"/>
+    <row r="527" ht="15.0" customHeight="1"/>
+    <row r="528" ht="15.0" customHeight="1"/>
+    <row r="529" ht="15.0" customHeight="1"/>
+    <row r="530" ht="15.0" customHeight="1"/>
+    <row r="531" ht="15.0" customHeight="1"/>
+    <row r="532" ht="15.0" customHeight="1"/>
+    <row r="533" ht="15.0" customHeight="1"/>
+    <row r="534" ht="15.0" customHeight="1"/>
+    <row r="535" ht="15.0" customHeight="1"/>
+    <row r="536" ht="15.0" customHeight="1"/>
+    <row r="537" ht="15.0" customHeight="1"/>
+    <row r="538" ht="15.0" customHeight="1"/>
+    <row r="539" ht="15.0" customHeight="1"/>
+    <row r="540" ht="15.0" customHeight="1"/>
+    <row r="541" ht="15.0" customHeight="1"/>
+    <row r="542" ht="15.0" customHeight="1"/>
+    <row r="543" ht="15.0" customHeight="1"/>
+    <row r="544" ht="15.0" customHeight="1"/>
+    <row r="545" ht="15.0" customHeight="1"/>
+    <row r="546" ht="15.0" customHeight="1"/>
+    <row r="547" ht="15.0" customHeight="1"/>
+    <row r="548" ht="15.0" customHeight="1"/>
+    <row r="549" ht="15.0" customHeight="1"/>
+    <row r="550" ht="15.0" customHeight="1"/>
+    <row r="551" ht="15.0" customHeight="1"/>
+    <row r="552" ht="15.0" customHeight="1"/>
+    <row r="553" ht="15.0" customHeight="1"/>
+    <row r="554" ht="15.0" customHeight="1"/>
+    <row r="555" ht="15.0" customHeight="1"/>
+    <row r="556" ht="15.0" customHeight="1"/>
+    <row r="557" ht="15.0" customHeight="1"/>
+    <row r="558" ht="15.0" customHeight="1"/>
+    <row r="559" ht="15.0" customHeight="1"/>
+    <row r="560" ht="15.0" customHeight="1"/>
+    <row r="561" ht="15.0" customHeight="1"/>
+    <row r="562" ht="15.0" customHeight="1"/>
+    <row r="563" ht="15.0" customHeight="1"/>
+    <row r="564" ht="15.0" customHeight="1"/>
+    <row r="565" ht="15.0" customHeight="1"/>
+    <row r="566" ht="15.0" customHeight="1"/>
+    <row r="567" ht="15.0" customHeight="1"/>
+    <row r="568" ht="15.0" customHeight="1"/>
+    <row r="569" ht="15.0" customHeight="1"/>
+    <row r="570" ht="15.0" customHeight="1"/>
+    <row r="571" ht="15.0" customHeight="1"/>
+    <row r="572" ht="15.0" customHeight="1"/>
+    <row r="573" ht="15.0" customHeight="1"/>
+    <row r="574" ht="15.0" customHeight="1"/>
+    <row r="575" ht="15.0" customHeight="1"/>
+    <row r="576" ht="15.0" customHeight="1"/>
+    <row r="577" ht="15.0" customHeight="1"/>
+    <row r="578" ht="15.0" customHeight="1"/>
+    <row r="579" ht="15.0" customHeight="1"/>
+    <row r="580" ht="15.0" customHeight="1"/>
+    <row r="581" ht="15.0" customHeight="1"/>
+    <row r="582" ht="15.0" customHeight="1"/>
+    <row r="583" ht="15.0" customHeight="1"/>
+    <row r="584" ht="15.0" customHeight="1"/>
+    <row r="585" ht="15.0" customHeight="1"/>
+    <row r="586" ht="15.0" customHeight="1"/>
+    <row r="587" ht="15.0" customHeight="1"/>
+    <row r="588" ht="15.0" customHeight="1"/>
+    <row r="589" ht="15.0" customHeight="1"/>
+    <row r="590" ht="15.0" customHeight="1"/>
+    <row r="591" ht="15.0" customHeight="1"/>
+    <row r="592" ht="15.0" customHeight="1"/>
+    <row r="593" ht="15.0" customHeight="1"/>
+    <row r="594" ht="15.0" customHeight="1"/>
+    <row r="595" ht="15.0" customHeight="1"/>
+    <row r="596" ht="15.0" customHeight="1"/>
+    <row r="597" ht="15.0" customHeight="1"/>
+    <row r="598" ht="15.0" customHeight="1"/>
+    <row r="599" ht="15.0" customHeight="1"/>
+    <row r="600" ht="15.0" customHeight="1"/>
+    <row r="601" ht="15.0" customHeight="1"/>
+    <row r="602" ht="15.0" customHeight="1"/>
+    <row r="603" ht="15.0" customHeight="1"/>
+    <row r="604" ht="15.0" customHeight="1"/>
+    <row r="605" ht="15.0" customHeight="1"/>
+    <row r="606" ht="15.0" customHeight="1"/>
+    <row r="607" ht="15.0" customHeight="1"/>
+    <row r="608" ht="15.0" customHeight="1"/>
+    <row r="609" ht="15.0" customHeight="1"/>
+    <row r="610" ht="15.0" customHeight="1"/>
+    <row r="611" ht="15.0" customHeight="1"/>
+    <row r="612" ht="15.0" customHeight="1"/>
+    <row r="613" ht="15.0" customHeight="1"/>
+    <row r="614" ht="15.0" customHeight="1"/>
+    <row r="615" ht="15.0" customHeight="1"/>
+    <row r="616" ht="15.0" customHeight="1"/>
+    <row r="617" ht="15.0" customHeight="1"/>
+    <row r="618" ht="15.0" customHeight="1"/>
+    <row r="619" ht="15.0" customHeight="1"/>
+    <row r="620" ht="15.0" customHeight="1"/>
+    <row r="621" ht="15.0" customHeight="1"/>
+    <row r="622" ht="15.0" customHeight="1"/>
+    <row r="623" ht="15.0" customHeight="1"/>
+    <row r="624" ht="15.0" customHeight="1"/>
+    <row r="625" ht="15.0" customHeight="1"/>
+    <row r="626" ht="15.0" customHeight="1"/>
+    <row r="627" ht="15.0" customHeight="1"/>
+    <row r="628" ht="15.0" customHeight="1"/>
+    <row r="629" ht="15.0" customHeight="1"/>
+    <row r="630" ht="15.0" customHeight="1"/>
+    <row r="631" ht="15.0" customHeight="1"/>
+    <row r="632" ht="15.0" customHeight="1"/>
+    <row r="633" ht="15.0" customHeight="1"/>
+    <row r="634" ht="15.0" customHeight="1"/>
+    <row r="635" ht="15.0" customHeight="1"/>
+    <row r="636" ht="15.0" customHeight="1"/>
+    <row r="637" ht="15.0" customHeight="1"/>
+    <row r="638" ht="15.0" customHeight="1"/>
+    <row r="639" ht="15.0" customHeight="1"/>
+    <row r="640" ht="15.0" customHeight="1"/>
+    <row r="641" ht="15.0" customHeight="1"/>
+    <row r="642" ht="15.0" customHeight="1"/>
+    <row r="643" ht="15.0" customHeight="1"/>
+    <row r="644" ht="15.0" customHeight="1"/>
+    <row r="645" ht="15.0" customHeight="1"/>
+    <row r="646" ht="15.0" customHeight="1"/>
+    <row r="647" ht="15.0" customHeight="1"/>
+    <row r="648" ht="15.0" customHeight="1"/>
+    <row r="649" ht="15.0" customHeight="1"/>
+    <row r="650" ht="15.0" customHeight="1"/>
+    <row r="651" ht="15.0" customHeight="1"/>
+    <row r="652" ht="15.0" customHeight="1"/>
+    <row r="653" ht="15.0" customHeight="1"/>
+    <row r="654" ht="15.0" customHeight="1"/>
+    <row r="655" ht="15.0" customHeight="1"/>
+    <row r="656" ht="15.0" customHeight="1"/>
+    <row r="657" ht="15.0" customHeight="1"/>
+    <row r="658" ht="15.0" customHeight="1"/>
+    <row r="659" ht="15.0" customHeight="1"/>
+    <row r="660" ht="15.0" customHeight="1"/>
+    <row r="661" ht="15.0" customHeight="1"/>
+    <row r="662" ht="15.0" customHeight="1"/>
+    <row r="663" ht="15.0" customHeight="1"/>
+    <row r="664" ht="15.0" customHeight="1"/>
+    <row r="665" ht="15.0" customHeight="1"/>
+    <row r="666" ht="15.0" customHeight="1"/>
+    <row r="667" ht="15.0" customHeight="1"/>
+    <row r="668" ht="15.0" customHeight="1"/>
+    <row r="669" ht="15.0" customHeight="1"/>
+    <row r="670" ht="15.0" customHeight="1"/>
+    <row r="671" ht="15.0" customHeight="1"/>
+    <row r="672" ht="15.0" customHeight="1"/>
+    <row r="673" ht="15.0" customHeight="1"/>
+    <row r="674" ht="15.0" customHeight="1"/>
+    <row r="675" ht="15.0" customHeight="1"/>
+    <row r="676" ht="15.0" customHeight="1"/>
+    <row r="677" ht="15.0" customHeight="1"/>
+    <row r="678" ht="15.0" customHeight="1"/>
+    <row r="679" ht="15.0" customHeight="1"/>
+    <row r="680" ht="15.0" customHeight="1"/>
+    <row r="681" ht="15.0" customHeight="1"/>
+    <row r="682" ht="15.0" customHeight="1"/>
+    <row r="683" ht="15.0" customHeight="1"/>
+    <row r="684" ht="15.0" customHeight="1"/>
+    <row r="685" ht="15.0" customHeight="1"/>
+    <row r="686" ht="15.0" customHeight="1"/>
+    <row r="687" ht="15.0" customHeight="1"/>
+    <row r="688" ht="15.0" customHeight="1"/>
+    <row r="689" ht="15.0" customHeight="1"/>
+    <row r="690" ht="15.0" customHeight="1"/>
+    <row r="691" ht="15.0" customHeight="1"/>
+    <row r="692" ht="15.0" customHeight="1"/>
+    <row r="693" ht="15.0" customHeight="1"/>
+    <row r="694" ht="15.0" customHeight="1"/>
+    <row r="695" ht="15.0" customHeight="1"/>
+    <row r="696" ht="15.0" customHeight="1"/>
+    <row r="697" ht="15.0" customHeight="1"/>
+    <row r="698" ht="15.0" customHeight="1"/>
+    <row r="699" ht="15.0" customHeight="1"/>
+    <row r="700" ht="15.0" customHeight="1"/>
+    <row r="701" ht="15.0" customHeight="1"/>
+    <row r="702" ht="15.0" customHeight="1"/>
+    <row r="703" ht="15.0" customHeight="1"/>
+    <row r="704" ht="15.0" customHeight="1"/>
+    <row r="705" ht="15.0" customHeight="1"/>
+    <row r="706" ht="15.0" customHeight="1"/>
+    <row r="707" ht="15.0" customHeight="1"/>
+    <row r="708" ht="15.0" customHeight="1"/>
+    <row r="709" ht="15.0" customHeight="1"/>
+    <row r="710" ht="15.0" customHeight="1"/>
+    <row r="711" ht="15.0" customHeight="1"/>
+    <row r="712" ht="15.0" customHeight="1"/>
+    <row r="713" ht="15.0" customHeight="1"/>
+    <row r="714" ht="15.0" customHeight="1"/>
+    <row r="715" ht="15.0" customHeight="1"/>
+    <row r="716" ht="15.0" customHeight="1"/>
+    <row r="717" ht="15.0" customHeight="1"/>
+    <row r="718" ht="15.0" customHeight="1"/>
+    <row r="719" ht="15.0" customHeight="1"/>
+    <row r="720" ht="15.0" customHeight="1"/>
+    <row r="721" ht="15.0" customHeight="1"/>
+    <row r="722" ht="15.0" customHeight="1"/>
+    <row r="723" ht="15.0" customHeight="1"/>
+    <row r="724" ht="15.0" customHeight="1"/>
+    <row r="725" ht="15.0" customHeight="1"/>
+    <row r="726" ht="15.0" customHeight="1"/>
+    <row r="727" ht="15.0" customHeight="1"/>
+    <row r="728" ht="15.0" customHeight="1"/>
+    <row r="729" ht="15.0" customHeight="1"/>
+    <row r="730" ht="15.0" customHeight="1"/>
+    <row r="731" ht="15.0" customHeight="1"/>
+    <row r="732" ht="15.0" customHeight="1"/>
+    <row r="733" ht="15.0" customHeight="1"/>
+    <row r="734" ht="15.0" customHeight="1"/>
+    <row r="735" ht="15.0" customHeight="1"/>
+    <row r="736" ht="15.0" customHeight="1"/>
+    <row r="737" ht="15.0" customHeight="1"/>
+    <row r="738" ht="15.0" customHeight="1"/>
+    <row r="739" ht="15.0" customHeight="1"/>
+    <row r="740" ht="15.0" customHeight="1"/>
+    <row r="741" ht="15.0" customHeight="1"/>
+    <row r="742" ht="15.0" customHeight="1"/>
+    <row r="743" ht="15.0" customHeight="1"/>
+    <row r="744" ht="15.0" customHeight="1"/>
+    <row r="745" ht="15.0" customHeight="1"/>
+    <row r="746" ht="15.0" customHeight="1"/>
+    <row r="747" ht="15.0" customHeight="1"/>
+    <row r="748" ht="15.0" customHeight="1"/>
+    <row r="749" ht="15.0" customHeight="1"/>
+    <row r="750" ht="15.0" customHeight="1"/>
+    <row r="751" ht="15.0" customHeight="1"/>
+    <row r="752" ht="15.0" customHeight="1"/>
+    <row r="753" ht="15.0" customHeight="1"/>
+    <row r="754" ht="15.0" customHeight="1"/>
+    <row r="755" ht="15.0" customHeight="1"/>
+    <row r="756" ht="15.0" customHeight="1"/>
+    <row r="757" ht="15.0" customHeight="1"/>
+    <row r="758" ht="15.0" customHeight="1"/>
+    <row r="759" ht="15.0" customHeight="1"/>
+    <row r="760" ht="15.0" customHeight="1"/>
+    <row r="761" ht="15.0" customHeight="1"/>
+    <row r="762" ht="15.0" customHeight="1"/>
+    <row r="763" ht="15.0" customHeight="1"/>
+    <row r="764" ht="15.0" customHeight="1"/>
+    <row r="765" ht="15.0" customHeight="1"/>
+    <row r="766" ht="15.0" customHeight="1"/>
+    <row r="767" ht="15.0" customHeight="1"/>
+    <row r="768" ht="15.0" customHeight="1"/>
+    <row r="769" ht="15.0" customHeight="1"/>
+    <row r="770" ht="15.0" customHeight="1"/>
+    <row r="771" ht="15.0" customHeight="1"/>
+    <row r="772" ht="15.0" customHeight="1"/>
+    <row r="773" ht="15.0" customHeight="1"/>
+    <row r="774" ht="15.0" customHeight="1"/>
+    <row r="775" ht="15.0" customHeight="1"/>
+    <row r="776" ht="15.0" customHeight="1"/>
+    <row r="777" ht="15.0" customHeight="1"/>
+    <row r="778" ht="15.0" customHeight="1"/>
+    <row r="779" ht="15.0" customHeight="1"/>
+    <row r="780" ht="15.0" customHeight="1"/>
+    <row r="781" ht="15.0" customHeight="1"/>
+    <row r="782" ht="15.0" customHeight="1"/>
+    <row r="783" ht="15.0" customHeight="1"/>
+    <row r="784" ht="15.0" customHeight="1"/>
+    <row r="785" ht="15.0" customHeight="1"/>
+    <row r="786" ht="15.0" customHeight="1"/>
+    <row r="787" ht="15.0" customHeight="1"/>
+    <row r="788" ht="15.0" customHeight="1"/>
+    <row r="789" ht="15.0" customHeight="1"/>
+    <row r="790" ht="15.0" customHeight="1"/>
+    <row r="791" ht="15.0" customHeight="1"/>
+    <row r="792" ht="15.0" customHeight="1"/>
+    <row r="793" ht="15.0" customHeight="1"/>
+    <row r="794" ht="15.0" customHeight="1"/>
+    <row r="795" ht="15.0" customHeight="1"/>
+    <row r="796" ht="15.0" customHeight="1"/>
+    <row r="797" ht="15.0" customHeight="1"/>
+    <row r="798" ht="15.0" customHeight="1"/>
+    <row r="799" ht="15.0" customHeight="1"/>
+    <row r="800" ht="15.0" customHeight="1"/>
+    <row r="801" ht="15.0" customHeight="1"/>
+    <row r="802" ht="15.0" customHeight="1"/>
+    <row r="803" ht="15.0" customHeight="1"/>
+    <row r="804" ht="15.0" customHeight="1"/>
+    <row r="805" ht="15.0" customHeight="1"/>
+    <row r="806" ht="15.0" customHeight="1"/>
+    <row r="807" ht="15.0" customHeight="1"/>
+    <row r="808" ht="15.0" customHeight="1"/>
+    <row r="809" ht="15.0" customHeight="1"/>
+    <row r="810" ht="15.0" customHeight="1"/>
+    <row r="811" ht="15.0" customHeight="1"/>
+    <row r="812" ht="15.0" customHeight="1"/>
+    <row r="813" ht="15.0" customHeight="1"/>
+    <row r="814" ht="15.0" customHeight="1"/>
+    <row r="815" ht="15.0" customHeight="1"/>
+    <row r="816" ht="15.0" customHeight="1"/>
+    <row r="817" ht="15.0" customHeight="1"/>
+    <row r="818" ht="15.0" customHeight="1"/>
+    <row r="819" ht="15.0" customHeight="1"/>
+    <row r="820" ht="15.0" customHeight="1"/>
+    <row r="821" ht="15.0" customHeight="1"/>
+    <row r="822" ht="15.0" customHeight="1"/>
+    <row r="823" ht="15.0" customHeight="1"/>
+    <row r="824" ht="15.0" customHeight="1"/>
+    <row r="825" ht="15.0" customHeight="1"/>
+    <row r="826" ht="15.0" customHeight="1"/>
+    <row r="827" ht="15.0" customHeight="1"/>
+    <row r="828" ht="15.0" customHeight="1"/>
+    <row r="829" ht="15.0" customHeight="1"/>
+    <row r="830" ht="15.0" customHeight="1"/>
+    <row r="831" ht="15.0" customHeight="1"/>
+    <row r="832" ht="15.0" customHeight="1"/>
+    <row r="833" ht="15.0" customHeight="1"/>
+    <row r="834" ht="15.0" customHeight="1"/>
+    <row r="835" ht="15.0" customHeight="1"/>
+    <row r="836" ht="15.0" customHeight="1"/>
+    <row r="837" ht="15.0" customHeight="1"/>
+    <row r="838" ht="15.0" customHeight="1"/>
+    <row r="839" ht="15.0" customHeight="1"/>
+    <row r="840" ht="15.0" customHeight="1"/>
+    <row r="841" ht="15.0" customHeight="1"/>
+    <row r="842" ht="15.0" customHeight="1"/>
+    <row r="843" ht="15.0" customHeight="1"/>
+    <row r="844" ht="15.0" customHeight="1"/>
+    <row r="845" ht="15.0" customHeight="1"/>
+    <row r="846" ht="15.0" customHeight="1"/>
+    <row r="847" ht="15.0" customHeight="1"/>
+    <row r="848" ht="15.0" customHeight="1"/>
+    <row r="849" ht="15.0" customHeight="1"/>
+    <row r="850" ht="15.0" customHeight="1"/>
+    <row r="851" ht="15.0" customHeight="1"/>
+    <row r="852" ht="15.0" customHeight="1"/>
+    <row r="853" ht="15.0" customHeight="1"/>
+    <row r="854" ht="15.0" customHeight="1"/>
+    <row r="855" ht="15.0" customHeight="1"/>
+    <row r="856" ht="15.0" customHeight="1"/>
+    <row r="857" ht="15.0" customHeight="1"/>
+    <row r="858" ht="15.0" customHeight="1"/>
+    <row r="859" ht="15.0" customHeight="1"/>
+    <row r="860" ht="15.0" customHeight="1"/>
+    <row r="861" ht="15.0" customHeight="1"/>
+    <row r="862" ht="15.0" customHeight="1"/>
+    <row r="863" ht="15.0" customHeight="1"/>
+    <row r="864" ht="15.0" customHeight="1"/>
+    <row r="865" ht="15.0" customHeight="1"/>
+    <row r="866" ht="15.0" customHeight="1"/>
+    <row r="867" ht="15.0" customHeight="1"/>
+    <row r="868" ht="15.0" customHeight="1"/>
+    <row r="869" ht="15.0" customHeight="1"/>
+    <row r="870" ht="15.0" customHeight="1"/>
+    <row r="871" ht="15.0" customHeight="1"/>
+    <row r="872" ht="15.0" customHeight="1"/>
+    <row r="873" ht="15.0" customHeight="1"/>
+    <row r="874" ht="15.0" customHeight="1"/>
+    <row r="875" ht="15.0" customHeight="1"/>
+    <row r="876" ht="15.0" customHeight="1"/>
+    <row r="877" ht="15.0" customHeight="1"/>
+    <row r="878" ht="15.0" customHeight="1"/>
+    <row r="879" ht="15.0" customHeight="1"/>
+    <row r="880" ht="15.0" customHeight="1"/>
+    <row r="881" ht="15.0" customHeight="1"/>
+    <row r="882" ht="15.0" customHeight="1"/>
+    <row r="883" ht="15.0" customHeight="1"/>
+    <row r="884" ht="15.0" customHeight="1"/>
+    <row r="885" ht="15.0" customHeight="1"/>
+    <row r="886" ht="15.0" customHeight="1"/>
+    <row r="887" ht="15.0" customHeight="1"/>
+    <row r="888" ht="15.0" customHeight="1"/>
+    <row r="889" ht="15.0" customHeight="1"/>
+    <row r="890" ht="15.0" customHeight="1"/>
+    <row r="891" ht="15.0" customHeight="1"/>
+    <row r="892" ht="15.0" customHeight="1"/>
+    <row r="893" ht="15.0" customHeight="1"/>
+    <row r="894" ht="15.0" customHeight="1"/>
+    <row r="895" ht="15.0" customHeight="1"/>
+    <row r="896" ht="15.0" customHeight="1"/>
+    <row r="897" ht="15.0" customHeight="1"/>
+    <row r="898" ht="15.0" customHeight="1"/>
+    <row r="899" ht="15.0" customHeight="1"/>
+    <row r="900" ht="15.0" customHeight="1"/>
+    <row r="901" ht="15.0" customHeight="1"/>
+    <row r="902" ht="15.0" customHeight="1"/>
+    <row r="903" ht="15.0" customHeight="1"/>
+    <row r="904" ht="15.0" customHeight="1"/>
+    <row r="905" ht="15.0" customHeight="1"/>
+    <row r="906" ht="15.0" customHeight="1"/>
+    <row r="907" ht="15.0" customHeight="1"/>
+    <row r="908" ht="15.0" customHeight="1"/>
+    <row r="909" ht="15.0" customHeight="1"/>
+    <row r="910" ht="15.0" customHeight="1"/>
+    <row r="911" ht="15.0" customHeight="1"/>
+    <row r="912" ht="15.0" customHeight="1"/>
+    <row r="913" ht="15.0" customHeight="1"/>
+    <row r="914" ht="15.0" customHeight="1"/>
+    <row r="915" ht="15.0" customHeight="1"/>
+    <row r="916" ht="15.0" customHeight="1"/>
+    <row r="917" ht="15.0" customHeight="1"/>
+    <row r="918" ht="15.0" customHeight="1"/>
+    <row r="919" ht="15.0" customHeight="1"/>
+    <row r="920" ht="15.0" customHeight="1"/>
+    <row r="921" ht="15.0" customHeight="1"/>
+    <row r="922" ht="15.0" customHeight="1"/>
+    <row r="923" ht="15.0" customHeight="1"/>
+    <row r="924" ht="15.0" customHeight="1"/>
+    <row r="925" ht="15.0" customHeight="1"/>
+    <row r="926" ht="15.0" customHeight="1"/>
+    <row r="927" ht="15.0" customHeight="1"/>
+    <row r="928" ht="15.0" customHeight="1"/>
+    <row r="929" ht="15.0" customHeight="1"/>
+    <row r="930" ht="15.0" customHeight="1"/>
+    <row r="931" ht="15.0" customHeight="1"/>
+    <row r="932" ht="15.0" customHeight="1"/>
+    <row r="933" ht="15.0" customHeight="1"/>
+    <row r="934" ht="15.0" customHeight="1"/>
+    <row r="935" ht="15.0" customHeight="1"/>
+    <row r="936" ht="15.0" customHeight="1"/>
+    <row r="937" ht="15.0" customHeight="1"/>
+    <row r="938" ht="15.0" customHeight="1"/>
+    <row r="939" ht="15.0" customHeight="1"/>
+    <row r="940" ht="15.0" customHeight="1"/>
+    <row r="941" ht="15.0" customHeight="1"/>
+    <row r="942" ht="15.0" customHeight="1"/>
+    <row r="943" ht="15.0" customHeight="1"/>
+    <row r="944" ht="15.0" customHeight="1"/>
+    <row r="945" ht="15.0" customHeight="1"/>
+    <row r="946" ht="15.0" customHeight="1"/>
+    <row r="947" ht="15.0" customHeight="1"/>
+    <row r="948" ht="15.0" customHeight="1"/>
+    <row r="949" ht="15.0" customHeight="1"/>
+    <row r="950" ht="15.0" customHeight="1"/>
+    <row r="951" ht="15.0" customHeight="1"/>
+    <row r="952" ht="15.0" customHeight="1"/>
+    <row r="953" ht="15.0" customHeight="1"/>
+    <row r="954" ht="15.0" customHeight="1"/>
+    <row r="955" ht="15.0" customHeight="1"/>
+    <row r="956" ht="15.0" customHeight="1"/>
+    <row r="957" ht="15.0" customHeight="1"/>
+    <row r="958" ht="15.0" customHeight="1"/>
+    <row r="959" ht="15.0" customHeight="1"/>
+    <row r="960" ht="15.0" customHeight="1"/>
+    <row r="961" ht="15.0" customHeight="1"/>
+    <row r="962" ht="15.0" customHeight="1"/>
+    <row r="963" ht="15.0" customHeight="1"/>
+    <row r="964" ht="15.0" customHeight="1"/>
+    <row r="965" ht="15.0" customHeight="1"/>
+    <row r="966" ht="15.0" customHeight="1"/>
+    <row r="967" ht="15.0" customHeight="1"/>
+    <row r="968" ht="15.0" customHeight="1"/>
+    <row r="969" ht="15.0" customHeight="1"/>
+    <row r="970" ht="15.0" customHeight="1"/>
+    <row r="971" ht="15.0" customHeight="1"/>
+    <row r="972" ht="15.0" customHeight="1"/>
+    <row r="973" ht="15.0" customHeight="1"/>
+    <row r="974" ht="15.0" customHeight="1"/>
+    <row r="975" ht="15.0" customHeight="1"/>
+    <row r="976" ht="15.0" customHeight="1"/>
+    <row r="977" ht="15.0" customHeight="1"/>
+    <row r="978" ht="15.0" customHeight="1"/>
+    <row r="979" ht="15.0" customHeight="1"/>
+    <row r="980" ht="15.0" customHeight="1"/>
+    <row r="981" ht="15.0" customHeight="1"/>
+    <row r="982" ht="15.0" customHeight="1"/>
+    <row r="983" ht="15.0" customHeight="1"/>
+    <row r="984" ht="15.0" customHeight="1"/>
+    <row r="985" ht="15.0" customHeight="1"/>
+    <row r="986" ht="15.0" customHeight="1"/>
+    <row r="987" ht="15.0" customHeight="1"/>
+    <row r="988" ht="15.0" customHeight="1"/>
+    <row r="989" ht="15.0" customHeight="1"/>
+    <row r="990" ht="15.0" customHeight="1"/>
+    <row r="991" ht="15.0" customHeight="1"/>
+    <row r="992" ht="15.0" customHeight="1"/>
+    <row r="993" ht="15.0" customHeight="1"/>
+    <row r="994" ht="15.0" customHeight="1"/>
+    <row r="995" ht="15.0" customHeight="1"/>
+    <row r="996" ht="15.0" customHeight="1"/>
+    <row r="997" ht="15.0" customHeight="1"/>
+    <row r="998" ht="15.0" customHeight="1"/>
+    <row r="999" ht="15.0" customHeight="1"/>
+    <row r="1000" ht="15.0" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/ResInfo/ResInfoTable.xlsx
+++ b/Templates/Tables/ResInfo/ResInfoTable.xlsx
@@ -300,7 +300,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="14.38"/>
+    <col customWidth="1" min="1" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">

--- a/Templates/Tables/ResInfo/ResInfoTable.xlsx
+++ b/Templates/Tables/ResInfo/ResInfoTable.xlsx
@@ -413,9 +413,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="8.13"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="28.63"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6230,9 +6233,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="9.38"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="21.88"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11997,9 +12003,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="11.5"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="9.38"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="15.5"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17782,9 +17791,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="9.38"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="34.75"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
